--- a/artfynd/A 10424-2026 artfynd.xlsx
+++ b/artfynd/A 10424-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123420681</v>
+        <v>123420679</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599884</v>
+        <v>599882</v>
       </c>
       <c r="R2" t="n">
-        <v>6832238</v>
+        <v>6832240</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +749,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_2428</t>
+          <t>2024_2430</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,15 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123420679</v>
+        <v>123420681</v>
       </c>
       <c r="B3" t="n">
-        <v>91299</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,21 +811,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -854,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599882</v>
+        <v>599884</v>
       </c>
       <c r="R3" t="n">
-        <v>6832240</v>
+        <v>6832238</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +874,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_2430</t>
+          <t>2024_2428</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -894,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -928,6 +918,126 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123420713</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kavelbromyran, Hls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>600008</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6832198</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Enånger</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2024_2405</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>07:05</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>07:05</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Samuel Koont, Stuart Fell</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Kustpaketet</t>
         </is>
